--- a/tmp/BullionView_Import_Template.xlsx
+++ b/tmp/BullionView_Import_Template.xlsx
@@ -655,7 +655,11 @@
           <t>premium_over_spot</t>
         </is>
       </c>
-      <c r="P4" s="3" t="n"/>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>sell_spread_over_spot</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n"/>
@@ -721,7 +725,7 @@
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr"/>
-      <c r="P5" s="3" t="n"/>
+      <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
